--- a/r4-ELGA-e-Medikation-BO_rework_use_case_2/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-BO_rework_use_case_2/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T15:46:37+00:00</t>
+    <t>2026-07-27T22:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-BO_rework_use_case_2/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-BO_rework_use_case_2/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:40:01+00:00</t>
+    <t>2026-07-27T23:37:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
